--- a/libertadores/datasets_liberta/times_1o_e_2o_lugar_fase_2.xlsx
+++ b/libertadores/datasets_liberta/times_1o_e_2o_lugar_fase_2.xlsx
@@ -91,7 +91,7 @@
     <t>lsauer fc</t>
   </si>
   <si>
-    <t>KillerColorado</t>
+    <t>Tabajara de Inhaua PB1</t>
   </si>
 </sst>
 </file>
@@ -764,31 +764,31 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>36359</v>
+        <v>28741323</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>986.1494140625</v>
+        <v>887.879638671875</v>
       </c>
       <c r="J9">
-        <v>451.849853515625</v>
+        <v>447.600341796875</v>
       </c>
       <c r="K9">
-        <v>534.299560546875</v>
+        <v>440.279296875</v>
       </c>
       <c r="L9">
         <v>2</v>
